--- a/artfynd/A 25573-2024 artfynd.xlsx
+++ b/artfynd/A 25573-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3007,6 +3007,600 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120148595</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90527</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långsvadmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>560872</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6630988</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120148492</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Långsvadmossen NV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>560734</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6631300</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120148567</v>
+      </c>
+      <c r="B22" t="n">
+        <v>89964</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Långsvadmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>560877</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6630976</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120148564</v>
+      </c>
+      <c r="B23" t="n">
+        <v>8432</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Långsvadmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>560902</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6630994</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120148591</v>
+      </c>
+      <c r="B24" t="n">
+        <v>90776</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1101</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gropticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Postia guttulata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Långsvadmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>560872</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6630988</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Tallstubbe</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25573-2024 artfynd.xlsx
+++ b/artfynd/A 25573-2024 artfynd.xlsx
@@ -3009,10 +3009,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120148595</v>
+        <v>120148591</v>
       </c>
       <c r="B20" t="n">
-        <v>90527</v>
+        <v>90776</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3021,25 +3021,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>1101</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Tallstubbe</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120148567</v>
+        <v>120148564</v>
       </c>
       <c r="B22" t="n">
-        <v>89964</v>
+        <v>8432</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3265,26 +3265,32 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5685</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3292,10 +3298,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560877</v>
+        <v>560902</v>
       </c>
       <c r="R22" t="n">
-        <v>6630976</v>
+        <v>6630994</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3365,10 +3371,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120148564</v>
+        <v>120148567</v>
       </c>
       <c r="B23" t="n">
-        <v>8432</v>
+        <v>89964</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3381,32 +3387,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>5685</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3414,10 +3414,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560902</v>
+        <v>560877</v>
       </c>
       <c r="R23" t="n">
-        <v>6630994</v>
+        <v>6630976</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120148591</v>
+        <v>120148595</v>
       </c>
       <c r="B24" t="n">
-        <v>90776</v>
+        <v>90527</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3499,25 +3499,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1101</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Tallstubbe</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 25573-2024 artfynd.xlsx
+++ b/artfynd/A 25573-2024 artfynd.xlsx
@@ -3009,10 +3009,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120148591</v>
+        <v>120148595</v>
       </c>
       <c r="B20" t="n">
-        <v>90776</v>
+        <v>90527</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3021,25 +3021,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1101</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Tallstubbe</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3125,10 +3125,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120148492</v>
+        <v>120148564</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>8432</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3137,54 +3137,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långsvadmossen NV, Vstm</t>
+          <t>Långsvadmossen, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560734</v>
+        <v>560902</v>
       </c>
       <c r="R21" t="n">
-        <v>6631300</v>
+        <v>6630994</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3231,7 +3224,12 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3249,10 +3247,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120148564</v>
+        <v>120148567</v>
       </c>
       <c r="B22" t="n">
-        <v>8432</v>
+        <v>89964</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3265,32 +3263,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>5685</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3298,10 +3290,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560902</v>
+        <v>560877</v>
       </c>
       <c r="R22" t="n">
-        <v>6630994</v>
+        <v>6630976</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3371,10 +3363,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120148567</v>
+        <v>120148591</v>
       </c>
       <c r="B23" t="n">
-        <v>89964</v>
+        <v>90776</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3383,25 +3375,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5685</v>
+        <v>1101</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3414,10 +3406,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560877</v>
+        <v>560872</v>
       </c>
       <c r="R23" t="n">
-        <v>6630976</v>
+        <v>6630988</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3469,7 +3461,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Tallstubbe</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3487,10 +3479,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120148595</v>
+        <v>120148492</v>
       </c>
       <c r="B24" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3499,41 +3491,54 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långsvadmossen, Vstm</t>
+          <t>Långsvadmossen NV, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560872</v>
+        <v>560734</v>
       </c>
       <c r="R24" t="n">
-        <v>6630988</v>
+        <v>6631300</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3580,12 +3585,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 25573-2024 artfynd.xlsx
+++ b/artfynd/A 25573-2024 artfynd.xlsx
@@ -3012,7 +3012,7 @@
         <v>120148595</v>
       </c>
       <c r="B20" t="n">
-        <v>90527</v>
+        <v>90545</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3125,10 +3125,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120148564</v>
+        <v>120148567</v>
       </c>
       <c r="B21" t="n">
-        <v>8432</v>
+        <v>89981</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3141,32 +3141,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>5685</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3174,10 +3168,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560902</v>
+        <v>560877</v>
       </c>
       <c r="R21" t="n">
-        <v>6630994</v>
+        <v>6630976</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3247,10 +3241,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120148567</v>
+        <v>120148564</v>
       </c>
       <c r="B22" t="n">
-        <v>89964</v>
+        <v>8432</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3263,26 +3257,32 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5685</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560877</v>
+        <v>560902</v>
       </c>
       <c r="R22" t="n">
-        <v>6630976</v>
+        <v>6630994</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3363,10 +3363,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120148591</v>
+        <v>120148492</v>
       </c>
       <c r="B23" t="n">
-        <v>90776</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3375,41 +3375,54 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1101</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långsvadmossen, Vstm</t>
+          <t>Långsvadmossen NV, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560872</v>
+        <v>560734</v>
       </c>
       <c r="R23" t="n">
-        <v>6630988</v>
+        <v>6631300</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3456,12 +3469,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Tallstubbe</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3479,10 +3487,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120148492</v>
+        <v>120148591</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>90794</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3491,54 +3499,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1101</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långsvadmossen NV, Vstm</t>
+          <t>Långsvadmossen, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560734</v>
+        <v>560872</v>
       </c>
       <c r="R24" t="n">
-        <v>6631300</v>
+        <v>6630988</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3585,7 +3580,12 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Tallstubbe</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 25573-2024 artfynd.xlsx
+++ b/artfynd/A 25573-2024 artfynd.xlsx
@@ -3009,10 +3009,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120148595</v>
+        <v>120148567</v>
       </c>
       <c r="B20" t="n">
-        <v>90545</v>
+        <v>89981</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3025,21 +3025,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>5685</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560872</v>
+        <v>560877</v>
       </c>
       <c r="R20" t="n">
-        <v>6630988</v>
+        <v>6630976</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3125,10 +3125,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120148567</v>
+        <v>120148564</v>
       </c>
       <c r="B21" t="n">
-        <v>89981</v>
+        <v>8432</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3141,26 +3141,32 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5685</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3168,10 +3174,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560877</v>
+        <v>560902</v>
       </c>
       <c r="R21" t="n">
-        <v>6630976</v>
+        <v>6630994</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3241,10 +3247,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120148564</v>
+        <v>120148591</v>
       </c>
       <c r="B22" t="n">
-        <v>8432</v>
+        <v>90794</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3253,36 +3259,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>1101</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560902</v>
+        <v>560872</v>
       </c>
       <c r="R22" t="n">
-        <v>6630994</v>
+        <v>6630988</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Tallstubbe</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120148591</v>
+        <v>120148595</v>
       </c>
       <c r="B24" t="n">
-        <v>90794</v>
+        <v>90545</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3499,25 +3499,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1101</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Tallstubbe</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 25573-2024 artfynd.xlsx
+++ b/artfynd/A 25573-2024 artfynd.xlsx
@@ -3009,10 +3009,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120148567</v>
+        <v>120148591</v>
       </c>
       <c r="B20" t="n">
-        <v>89981</v>
+        <v>90794</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3021,25 +3021,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5685</v>
+        <v>1101</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560877</v>
+        <v>560872</v>
       </c>
       <c r="R20" t="n">
-        <v>6630976</v>
+        <v>6630988</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Tallstubbe</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3125,10 +3125,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120148564</v>
+        <v>120148595</v>
       </c>
       <c r="B21" t="n">
-        <v>8432</v>
+        <v>90545</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3141,32 +3141,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3174,10 +3168,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560902</v>
+        <v>560872</v>
       </c>
       <c r="R21" t="n">
-        <v>6630994</v>
+        <v>6630988</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3229,7 +3223,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3247,10 +3241,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120148591</v>
+        <v>120148564</v>
       </c>
       <c r="B22" t="n">
-        <v>90794</v>
+        <v>8432</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3259,30 +3253,36 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1101</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560872</v>
+        <v>560902</v>
       </c>
       <c r="R22" t="n">
-        <v>6630988</v>
+        <v>6630994</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Tallstubbe</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120148595</v>
+        <v>120148567</v>
       </c>
       <c r="B24" t="n">
-        <v>90545</v>
+        <v>89981</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3503,21 +3503,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>5685</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3530,10 +3530,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560872</v>
+        <v>560877</v>
       </c>
       <c r="R24" t="n">
-        <v>6630988</v>
+        <v>6630976</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 25573-2024 artfynd.xlsx
+++ b/artfynd/A 25573-2024 artfynd.xlsx
@@ -3009,10 +3009,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120148591</v>
+        <v>120148567</v>
       </c>
       <c r="B20" t="n">
-        <v>90794</v>
+        <v>89981</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3021,25 +3021,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1101</v>
+        <v>5685</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560872</v>
+        <v>560877</v>
       </c>
       <c r="R20" t="n">
-        <v>6630988</v>
+        <v>6630976</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Tallstubbe</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3363,10 +3363,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120148492</v>
+        <v>120148591</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>90794</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3375,54 +3375,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1101</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långsvadmossen NV, Vstm</t>
+          <t>Långsvadmossen, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560734</v>
+        <v>560872</v>
       </c>
       <c r="R23" t="n">
-        <v>6631300</v>
+        <v>6630988</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3469,7 +3456,12 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Tallstubbe</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3487,10 +3479,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120148567</v>
+        <v>120148492</v>
       </c>
       <c r="B24" t="n">
-        <v>89981</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3499,41 +3491,54 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5685</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långsvadmossen, Vstm</t>
+          <t>Långsvadmossen NV, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560877</v>
+        <v>560734</v>
       </c>
       <c r="R24" t="n">
-        <v>6630976</v>
+        <v>6631300</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3580,12 +3585,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Tall</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 25573-2024 artfynd.xlsx
+++ b/artfynd/A 25573-2024 artfynd.xlsx
@@ -3125,10 +3125,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120148595</v>
+        <v>120148492</v>
       </c>
       <c r="B21" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3137,41 +3137,54 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långsvadmossen, Vstm</t>
+          <t>Långsvadmossen NV, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560872</v>
+        <v>560734</v>
       </c>
       <c r="R21" t="n">
-        <v>6630988</v>
+        <v>6631300</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3218,12 +3231,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3241,10 +3249,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120148564</v>
+        <v>120148595</v>
       </c>
       <c r="B22" t="n">
-        <v>8432</v>
+        <v>90545</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3257,32 +3265,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3290,10 +3292,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560902</v>
+        <v>560872</v>
       </c>
       <c r="R22" t="n">
-        <v>6630994</v>
+        <v>6630988</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3345,7 +3347,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3363,10 +3365,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120148591</v>
+        <v>120148564</v>
       </c>
       <c r="B23" t="n">
-        <v>90794</v>
+        <v>8432</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3375,30 +3377,36 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1101</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3406,10 +3414,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560872</v>
+        <v>560902</v>
       </c>
       <c r="R23" t="n">
-        <v>6630988</v>
+        <v>6630994</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3461,7 +3469,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Tallstubbe</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3479,10 +3487,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120148492</v>
+        <v>120148591</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>90794</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3491,54 +3499,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1101</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långsvadmossen NV, Vstm</t>
+          <t>Långsvadmossen, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560734</v>
+        <v>560872</v>
       </c>
       <c r="R24" t="n">
-        <v>6631300</v>
+        <v>6630988</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3585,7 +3580,12 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Tallstubbe</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 25573-2024 artfynd.xlsx
+++ b/artfynd/A 25573-2024 artfynd.xlsx
@@ -3009,10 +3009,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120148567</v>
+        <v>120148492</v>
       </c>
       <c r="B20" t="n">
-        <v>89981</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3021,41 +3021,54 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5685</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långsvadmossen, Vstm</t>
+          <t>Långsvadmossen NV, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560877</v>
+        <v>560734</v>
       </c>
       <c r="R20" t="n">
-        <v>6630976</v>
+        <v>6631300</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3102,12 +3115,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Tall</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3125,10 +3133,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120148492</v>
+        <v>120148595</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3137,54 +3145,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långsvadmossen NV, Vstm</t>
+          <t>Långsvadmossen, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560734</v>
+        <v>560872</v>
       </c>
       <c r="R21" t="n">
-        <v>6631300</v>
+        <v>6630988</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3231,7 +3226,12 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120148595</v>
+        <v>120148567</v>
       </c>
       <c r="B22" t="n">
-        <v>90545</v>
+        <v>89981</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3265,21 +3265,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>5685</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560872</v>
+        <v>560877</v>
       </c>
       <c r="R22" t="n">
-        <v>6630988</v>
+        <v>6630976</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120148564</v>
+        <v>120148591</v>
       </c>
       <c r="B23" t="n">
-        <v>8432</v>
+        <v>90794</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3377,36 +3377,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>1101</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3414,10 +3408,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560902</v>
+        <v>560872</v>
       </c>
       <c r="R23" t="n">
-        <v>6630994</v>
+        <v>6630988</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3469,7 +3463,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Tallstubbe</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3487,10 +3481,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120148591</v>
+        <v>120148564</v>
       </c>
       <c r="B24" t="n">
-        <v>90794</v>
+        <v>8432</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3499,30 +3493,36 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1101</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3530,10 +3530,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560872</v>
+        <v>560902</v>
       </c>
       <c r="R24" t="n">
-        <v>6630988</v>
+        <v>6630994</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Tallstubbe</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 25573-2024 artfynd.xlsx
+++ b/artfynd/A 25573-2024 artfynd.xlsx
@@ -3249,10 +3249,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120148567</v>
+        <v>120148591</v>
       </c>
       <c r="B22" t="n">
-        <v>89981</v>
+        <v>90794</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3261,25 +3261,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5685</v>
+        <v>1101</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560877</v>
+        <v>560872</v>
       </c>
       <c r="R22" t="n">
-        <v>6630976</v>
+        <v>6630988</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Tallstubbe</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120148591</v>
+        <v>120148564</v>
       </c>
       <c r="B23" t="n">
-        <v>90794</v>
+        <v>8432</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3377,30 +3377,36 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1101</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3408,10 +3414,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560872</v>
+        <v>560902</v>
       </c>
       <c r="R23" t="n">
-        <v>6630988</v>
+        <v>6630994</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3463,7 +3469,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Tallstubbe</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3481,10 +3487,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120148564</v>
+        <v>120148567</v>
       </c>
       <c r="B24" t="n">
-        <v>8432</v>
+        <v>89981</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3497,32 +3503,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>5685</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3530,10 +3530,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560902</v>
+        <v>560877</v>
       </c>
       <c r="R24" t="n">
-        <v>6630994</v>
+        <v>6630976</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 25573-2024 artfynd.xlsx
+++ b/artfynd/A 25573-2024 artfynd.xlsx
@@ -3869,7 +3869,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124264379</v>
+        <v>124264731</v>
       </c>
       <c r="B27" t="n">
         <v>8447</v>
@@ -3910,14 +3910,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Acktjärnsåsen, Acktjärnsåsen, Vstm</t>
+          <t>Acktjärnsskogen, Ramnäs, Vstm, Acktjärnsskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560720</v>
+        <v>560728</v>
       </c>
       <c r="R27" t="n">
-        <v>6631141</v>
+        <v>6631238</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3991,7 +3991,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124264731</v>
+        <v>124264379</v>
       </c>
       <c r="B28" t="n">
         <v>8447</v>
@@ -4032,14 +4032,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Acktjärnsskogen, Ramnäs, Vstm, Acktjärnsskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Acktjärnsåsen, Acktjärnsåsen, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560728</v>
+        <v>560720</v>
       </c>
       <c r="R28" t="n">
-        <v>6631238</v>
+        <v>6631141</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 25573-2024 artfynd.xlsx
+++ b/artfynd/A 25573-2024 artfynd.xlsx
@@ -3869,7 +3869,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124264731</v>
+        <v>124264379</v>
       </c>
       <c r="B27" t="n">
         <v>8447</v>
@@ -3910,14 +3910,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Acktjärnsskogen, Ramnäs, Vstm, Acktjärnsskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Acktjärnsåsen, Acktjärnsåsen, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560728</v>
+        <v>560720</v>
       </c>
       <c r="R27" t="n">
-        <v>6631238</v>
+        <v>6631141</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3991,7 +3991,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124264379</v>
+        <v>124264731</v>
       </c>
       <c r="B28" t="n">
         <v>8447</v>
@@ -4032,14 +4032,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Acktjärnsåsen, Acktjärnsåsen, Vstm</t>
+          <t>Acktjärnsskogen, Ramnäs, Vstm, Acktjärnsskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560720</v>
+        <v>560728</v>
       </c>
       <c r="R28" t="n">
-        <v>6631141</v>
+        <v>6631238</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 25573-2024 artfynd.xlsx
+++ b/artfynd/A 25573-2024 artfynd.xlsx
@@ -3603,10 +3603,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124208101</v>
+        <v>124205765</v>
       </c>
       <c r="B25" t="n">
-        <v>8447</v>
+        <v>105117</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3619,46 +3619,53 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Acktjärnsskogen, Ramnäs, Acktjärnsskogen, Ramnäs, Vstm</t>
+          <t>Acktjärnsåsarna, Ramnäs,, Acktjärnsåsarna, Ramnäs,, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>561134</v>
+        <v>561038</v>
       </c>
       <c r="R25" t="n">
-        <v>6631681</v>
+        <v>6631445</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3687,7 +3694,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3697,7 +3704,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3713,6 +3720,11 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Äldre granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3730,10 +3742,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124205765</v>
+        <v>124208101</v>
       </c>
       <c r="B26" t="n">
-        <v>105117</v>
+        <v>8447</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3746,53 +3758,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Acktjärnsåsarna, Ramnäs,, Acktjärnsåsarna, Ramnäs,, Vstm</t>
+          <t>Acktjärnsskogen, Ramnäs, Acktjärnsskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>561038</v>
+        <v>561134</v>
       </c>
       <c r="R26" t="n">
-        <v>6631445</v>
+        <v>6631681</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3821,7 +3826,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3831,7 +3836,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3847,11 +3852,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Äldre granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 25573-2024 artfynd.xlsx
+++ b/artfynd/A 25573-2024 artfynd.xlsx
@@ -3603,10 +3603,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124205765</v>
+        <v>124208101</v>
       </c>
       <c r="B25" t="n">
-        <v>105117</v>
+        <v>8447</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3619,53 +3619,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Acktjärnsåsarna, Ramnäs,, Acktjärnsåsarna, Ramnäs,, Vstm</t>
+          <t>Acktjärnsskogen, Ramnäs, Acktjärnsskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>561038</v>
+        <v>561134</v>
       </c>
       <c r="R25" t="n">
-        <v>6631445</v>
+        <v>6631681</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3694,7 +3687,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3704,7 +3697,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3720,11 +3713,6 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Äldre granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3742,10 +3730,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124208101</v>
+        <v>124205765</v>
       </c>
       <c r="B26" t="n">
-        <v>8447</v>
+        <v>105117</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3758,46 +3746,53 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Acktjärnsskogen, Ramnäs, Acktjärnsskogen, Ramnäs, Vstm</t>
+          <t>Acktjärnsåsarna, Ramnäs,, Acktjärnsåsarna, Ramnäs,, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>561134</v>
+        <v>561038</v>
       </c>
       <c r="R26" t="n">
-        <v>6631681</v>
+        <v>6631445</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3826,7 +3821,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3836,7 +3831,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3852,6 +3847,11 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Äldre granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 25573-2024 artfynd.xlsx
+++ b/artfynd/A 25573-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73056920</v>
+        <v>120148591</v>
       </c>
       <c r="B2" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,44 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>1101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långsvadmossen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560923.6128033072</v>
+        <v>560872</v>
       </c>
       <c r="R2" t="n">
-        <v>6631028.27520666</v>
+        <v>6630988</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-09-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-09-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,12 +763,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog, gränsande till tallmosse</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Mager hällmark</t>
+          <t>Tallstubbe</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -808,59 +786,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73056826</v>
+        <v>103508291</v>
       </c>
       <c r="B3" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>1106</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långsvadmossen V, Vstm</t>
+          <t>Långsvadmossen NV, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560796.8653308095</v>
+        <v>560825</v>
       </c>
       <c r="R3" t="n">
-        <v>6631012.615829467</v>
+        <v>6631124</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,22 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-09-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-09-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,12 +874,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -940,42 +897,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73056928</v>
+        <v>73056920</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -990,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560923.6128033072</v>
+        <v>560924</v>
       </c>
       <c r="R4" t="n">
-        <v>6631028.27520666</v>
+        <v>6631028</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,19 +975,9 @@
           <t>2018-09-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-09-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,52 +1015,56 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73056723</v>
+        <v>103508212</v>
       </c>
       <c r="B5" t="n">
-        <v>89780</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långsvadmossen V, Vstm</t>
+          <t>Långsvadmossen, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560796.8653308095</v>
+        <v>560931</v>
       </c>
       <c r="R5" t="n">
-        <v>6631012.615829467</v>
+        <v>6631025</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1145,22 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-09-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-09-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,12 +1111,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Tallåga, på undersidan</t>
+          <t>Hällmarksudde i mosse</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1198,62 +1129,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103507886</v>
+        <v>73056723</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långsvadmossen NV, Vstm</t>
+          <t>Långsvadmossen V, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560872.541928368</v>
+        <v>560797</v>
       </c>
       <c r="R6" t="n">
-        <v>6631192.460038925</v>
+        <v>6631013</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1280,22 +1196,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1310,7 +1216,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrblandskog, inslag av björk</t>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Tallåga, på undersidan</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1328,37 +1239,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103507982</v>
+        <v>73056928</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1368,22 +1274,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långsvadmossen NV, Vstm</t>
+          <t>Långsvadmossen, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560887.1623867544</v>
+        <v>560924</v>
       </c>
       <c r="R7" t="n">
-        <v>6631222.885541609</v>
+        <v>6631028</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1410,22 +1314,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1440,7 +1334,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrblandskog, inslag av björk</t>
+          <t>Hällmarkstallskog, gränsande till tallmosse</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Mager hällmark</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1458,48 +1357,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103508256</v>
+        <v>103508148</v>
       </c>
       <c r="B8" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1507,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560825.2774972187</v>
+        <v>560941</v>
       </c>
       <c r="R8" t="n">
-        <v>6631124.269981397</v>
+        <v>6631070</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1540,19 +1428,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1567,12 +1445,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Tall</t>
+          <t>Barrblandskog, hällmarker</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1590,66 +1463,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103507877</v>
+        <v>103508222</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långsvadmossen NV, Vstm</t>
+          <t>Långsvadmossen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560870.3783809199</v>
+        <v>560931</v>
       </c>
       <c r="R9" t="n">
-        <v>6631201.480453818</v>
+        <v>6631025</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1679,19 +1534,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1706,7 +1551,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Barrblandskog, inslag av björk</t>
+          <t>Hällmarksudde i mosse</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1724,66 +1569,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103507970</v>
+        <v>120148595</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långsvadmossen NV, Vstm</t>
+          <t>Långsvadmossen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560801.7698259659</v>
+        <v>560872</v>
       </c>
       <c r="R10" t="n">
-        <v>6631236.580779156</v>
+        <v>6630988</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1810,22 +1637,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1840,7 +1657,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Barrblandskog, inslag av björk</t>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1858,62 +1680,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103507916</v>
+        <v>120148567</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5685</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långsvadmossen NV, Vstm</t>
+          <t>Långsvadmossen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560802.9420006039</v>
+        <v>560877</v>
       </c>
       <c r="R11" t="n">
-        <v>6631226.538004628</v>
+        <v>6630976</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1940,22 +1748,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1970,7 +1768,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrblandskog, inslag av björk</t>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1988,37 +1791,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103508148</v>
+        <v>112398391</v>
       </c>
       <c r="B12" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2027,14 +1825,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långsvadmossen, Vstm</t>
+          <t>Långsvadmossen N, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560941.0669386139</v>
+        <v>561238</v>
       </c>
       <c r="R12" t="n">
-        <v>6631070.320464399</v>
+        <v>6631361</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2061,22 +1859,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2091,7 +1879,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmarker</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2109,59 +1897,56 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103508160</v>
+        <v>112401627</v>
       </c>
       <c r="B13" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långsvadmossen, Vstm</t>
+          <t>Långsvadmossen N, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560941.0669386139</v>
+        <v>560910</v>
       </c>
       <c r="R13" t="n">
-        <v>6631070.320464399</v>
+        <v>6631389</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2188,22 +1973,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2219,11 +1994,6 @@
       <c r="AI13" t="inlineStr">
         <is>
           <t>Barrblandskog, hällmarker</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Tall</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2241,66 +2011,56 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103508331</v>
+        <v>120148521</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långsvadmossen NV, Vstm</t>
+          <t>Långsvadmossen N, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560825.2774972187</v>
+        <v>560926</v>
       </c>
       <c r="R14" t="n">
-        <v>6631124.269981397</v>
+        <v>6631147</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2327,22 +2087,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2+1</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2357,7 +2112,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2375,53 +2130,61 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103508291</v>
+        <v>118342155</v>
       </c>
       <c r="B15" t="n">
-        <v>89588</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1106</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långsvadmossen NV, Vstm</t>
+          <t>Acktjärnsskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560825.2774972187</v>
+        <v>560925</v>
       </c>
       <c r="R15" t="n">
-        <v>6631124.269981397</v>
+        <v>6631285</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2448,22 +2211,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2472,93 +2235,82 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>Gran/tallskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors, Sören Larsson, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104689775</v>
+        <v>73056826</v>
       </c>
       <c r="B16" t="n">
-        <v>108203</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219716</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Krusfrö</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Selinum carvifolia</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långsvadsmossen, NV (krusfrö), Vstm</t>
+          <t>Långsvadmossen V, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560801.7698259659</v>
+        <v>560797</v>
       </c>
       <c r="R16" t="n">
-        <v>6631236.580779156</v>
+        <v>6631013</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2583,29 +2335,14 @@
           <t>Ramnäs</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>U-Sur-0507</t>
-        </is>
-      </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2614,18 +2351,24 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>barrblandskog inslag av björk</t>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -2633,61 +2376,58 @@
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112398391</v>
+        <v>103508160</v>
       </c>
       <c r="B17" t="n">
-        <v>90937</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långsvadmossen N, Vstm</t>
+          <t>Långsvadmossen, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>561238</v>
+        <v>560941</v>
       </c>
       <c r="R17" t="n">
-        <v>6631361</v>
+        <v>6631070</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2714,12 +2454,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2734,7 +2474,12 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Barrblandskog, hällmarker</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2752,61 +2497,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112401627</v>
+        <v>103508256</v>
       </c>
       <c r="B18" t="n">
-        <v>90937</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långsvadmossen N, Vstm</t>
+          <t>Långsvadmossen, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560910</v>
+        <v>560825</v>
       </c>
       <c r="R18" t="n">
-        <v>6631389</v>
+        <v>6631124</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2833,12 +2571,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2853,7 +2591,12 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmarker</t>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2871,66 +2614,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118342155</v>
+        <v>120148564</v>
       </c>
       <c r="B19" t="n">
-        <v>57445</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Acktjärnsskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Långsvadmossen, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560925</v>
+        <v>560902</v>
       </c>
       <c r="R19" t="n">
-        <v>6631285</v>
+        <v>6630994</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2957,22 +2688,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2981,97 +2702,86 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Gran/tallskog</t>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Sören Larsson, Bengt Eriksson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120148492</v>
+        <v>124208101</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långsvadmossen NV, Vstm</t>
+          <t>Acktjärnsskogen, Ramnäs, Acktjärnsskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560734</v>
+        <v>561134</v>
       </c>
       <c r="R20" t="n">
-        <v>6631300</v>
+        <v>6631681</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3095,12 +2805,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3113,35 +2833,30 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120148595</v>
+        <v>124264379</v>
       </c>
       <c r="B21" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3149,40 +2864,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långsvadmossen, Vstm</t>
+          <t>Acktjärnsåsen, Acktjärnsåsen, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560872</v>
+        <v>560720</v>
       </c>
       <c r="R21" t="n">
-        <v>6630988</v>
+        <v>6631141</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3206,12 +2923,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3220,85 +2947,76 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Gran</t>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120148591</v>
+        <v>124264731</v>
       </c>
       <c r="B22" t="n">
-        <v>90794</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1101</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långsvadmossen, Vstm</t>
+          <t>Acktjärnsskogen, Ramnäs, Vstm, Acktjärnsskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560872</v>
+        <v>560728</v>
       </c>
       <c r="R22" t="n">
-        <v>6630988</v>
+        <v>6631238</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3322,12 +3040,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3336,88 +3064,82 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Tallstubbe</t>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120148564</v>
+        <v>104689775</v>
       </c>
       <c r="B23" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111399</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>219716</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Krusfrö</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Selinum carvifolia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>(L.) L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långsvadmossen, Vstm</t>
+          <t>Långsvadsmossen, NV (krusfrö), Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560902</v>
+        <v>560802</v>
       </c>
       <c r="R23" t="n">
-        <v>6630994</v>
+        <v>6631237</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3442,14 +3164,19 @@
           <t>Ramnäs</t>
         </is>
       </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>U-Sur-0507</t>
+        </is>
+      </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3458,24 +3185,18 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Tall</t>
+          <t>barrblandskog inslag av björk</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Bo Eriksson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -3483,57 +3204,69 @@
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120148567</v>
+        <v>103507877</v>
       </c>
       <c r="B24" t="n">
-        <v>89981</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5685</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långsvadmossen, Vstm</t>
+          <t>Långsvadmossen NV, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560877</v>
+        <v>560870</v>
       </c>
       <c r="R24" t="n">
-        <v>6630976</v>
+        <v>6631201</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3560,12 +3293,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3580,12 +3313,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Tall</t>
+          <t>Barrblandskog, inslag av björk</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3603,42 +3331,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124205765</v>
+        <v>103507886</v>
       </c>
       <c r="B25" t="n">
-        <v>105117</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3646,26 +3369,22 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Acktjärnsåsarna, Ramnäs,, Acktjärnsåsarna, Ramnäs,, Vstm</t>
+          <t>Långsvadmossen NV, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>561038</v>
+        <v>560873</v>
       </c>
       <c r="R25" t="n">
-        <v>6631445</v>
+        <v>6631192</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3689,22 +3408,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>16:39</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>16:39</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3717,87 +3426,80 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Äldre granskog</t>
+          <t>Barrblandskog, inslag av björk</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124208101</v>
+        <v>103507916</v>
       </c>
       <c r="B26" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Acktjärnsskogen, Ramnäs, Acktjärnsskogen, Ramnäs, Vstm</t>
+          <t>Långsvadmossen NV, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>561134</v>
+        <v>560803</v>
       </c>
       <c r="R26" t="n">
-        <v>6631681</v>
+        <v>6631227</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3821,22 +3523,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>17:32</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>17:32</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3849,78 +3541,84 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Barrblandskog, inslag av björk</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124264731</v>
+        <v>103507970</v>
       </c>
       <c r="B27" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Acktjärnsskogen, Ramnäs, Vstm, Acktjärnsskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Långsvadmossen NV, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560728</v>
+        <v>560802</v>
       </c>
       <c r="R27" t="n">
-        <v>6631238</v>
+        <v>6631237</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3944,22 +3642,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:34</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:34</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3968,81 +3656,84 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Häll- och blockskog</t>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Barrblandskog, inslag av björk</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124264379</v>
+        <v>103507982</v>
       </c>
       <c r="B28" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Acktjärnsåsen, Acktjärnsåsen, Vstm</t>
+          <t>Långsvadmossen NV, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560720</v>
+        <v>560887</v>
       </c>
       <c r="R28" t="n">
-        <v>6631141</v>
+        <v>6631223</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4066,22 +3757,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4090,26 +3771,399 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Häll- och blockskog</t>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Barrblandskog, inslag av björk</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>103508331</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Långsvadmossen NV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>560825</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6631124</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2022-09-09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2022-09-09</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120148492</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Långsvadmossen NV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>560734</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6631300</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>124205765</v>
+      </c>
+      <c r="B31" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Acktjärnsåsarna, Ramnäs,, Acktjärnsåsarna, Ramnäs,, Vstm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>561038</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6631445</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Äldre granskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
+      <c r="AX31" t="inlineStr">
         <is>
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
